--- a/outputs/daily/hr_rankings_2026-08-08_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-08_remaining.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
